--- a/output/2026-09-20_01_Croazia_Šibensko-kninska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-20_01_Croazia_Šibensko-kninska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -578,7 +578,6 @@
           <t>022 443 044</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Negozio/distributore di materiali edili, utensili per muratori e carpentieri, ferramenta e materiale elettrico. Esistenza confermata da directory aziendali (companywall.hr, tvrtke.hr, mojkvart.hr, emajstor.hr). Indirizzo confermato: Put Gaćeleza 1 / Obala Ive Juričeva Cote 9, 22211 Vodice. Nessuna email trovata: campo lasciato vuoto.</t>
@@ -616,10 +615,9 @@
           <t>072 446 622</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Punto vendita locale della catena nazionale Pevex (Pevex d.o.o.), con reparto 'Željeznarija' dedicato a utensili manuali ed elettrici e attrezzature. Esistenza, indirizzo (Ul. Velimira Škorpika 23, 22000 Šibenik) e telefono confermati tramite più fonti (pevex.hr, mojkatalog.hr, hr.polomap.com, katalog24.hr). Si tratta di un punto vendita di una catena nazionale, non di un'azienda autonoma con sede legale propria a Šibenik. Email di contatto non verificabile con certezza (mascherata nei risultati di ricerca): campo lasciato vuoto.</t>
+          <t>Punto vendita locale della catena nazionale Pevex (Pevex d.o.o.), con reparto 'Željeznarija' dedicato a utensili manuali ed elettrici e attrezzature. Esistenza, indirizzo (Ul. Velimira Škorpika 23, 22000 Šibenik) e telefono confermati tramite più fonti (pevex.hr, mojkatalog.hr, hr.polomap.com, katalog24.hr). Si tratta di un punto vendita di una catena nazionale, non di un'azienda autonoma con sede legale propria a Šibenik. Email di contatto non verificabile con certezza (mascherata nei risultati di ricerca): campo lasciato vuoto. [DUPLICATO — vedi anche: 2026-09-19_21_Croazia_Sibensko-kninska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">

--- a/output/2026-09-20_01_Croazia_Šibensko-kninska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-20_01_Croazia_Šibensko-kninska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
